--- a/新鸿社区86-29-三单元_水费+垃圾费记录.xlsx
+++ b/新鸿社区86-29-三单元_水费+垃圾费记录.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\GIT SYNC\default\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AB43C7A-C2D9-4B70-AEF9-05115204299F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B3DDF28-BD28-40AF-9A06-C92566C98F7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="每户水表记录" sheetId="1" r:id="rId1"/>
+    <sheet name="2026-08" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,8 +30,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
   <si>
     <t>门号</t>
   </si>
@@ -159,6 +181,10 @@
     <t>实际抄表每方费用</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>状态</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -167,7 +193,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -331,6 +357,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -370,7 +403,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -505,61 +538,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -621,19 +607,34 @@
     <xf numFmtId="2" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="12" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -699,14 +700,17 @@
     <xf numFmtId="2" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="12" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -932,15 +936,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="40.049999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -962,32 +966,34 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="18" t="s">
         <v>6</v>
       </c>
       <c r="H2" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="2" t="s">
+      <c r="I2" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="22" t="s">
         <v>13</v>
       </c>
       <c r="K2" s="1"/>
@@ -1008,35 +1014,38 @@
       <c r="Z2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="6">
+      <c r="A3" s="4">
         <v>1</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="5">
         <v>2123</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="5">
         <v>2130</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="5">
         <f t="shared" ref="D3:D14" si="0">C3-B3</f>
         <v>7</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="6">
         <f>E$15 * (D3/D$15)</f>
         <v>25.956293706293707</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="5">
         <v>10.7</v>
       </c>
-      <c r="G3" s="33">
+      <c r="G3" s="36">
         <f>SUM(E3,F3,E4,F4)</f>
         <v>154.88951048951049</v>
       </c>
-      <c r="H3" s="27">
+      <c r="H3" s="31">
         <v>0</v>
       </c>
-      <c r="I3" s="1"/>
-      <c r="J3" s="3">
+      <c r="I3" s="30" t="str" cm="1">
+        <f t="array" ref="I3">_xlfn.IFS(ABS(G3-H3)&lt;0.1, "已收", G3&lt;H3, "多了", G3&gt;H3, "不够", H3=0, "没交")</f>
+        <v>不够</v>
+      </c>
+      <c r="J3" s="23">
         <v>-5</v>
       </c>
       <c r="K3" s="1"/>
@@ -1057,30 +1066,30 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="6">
+      <c r="A4" s="4">
         <v>2</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="5">
         <v>5279</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="5">
         <v>5308</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="5">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="6">
         <f>E$15 * (D4/D$15)</f>
         <v>107.53321678321677</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="5">
         <v>10.7</v>
       </c>
-      <c r="G4" s="34"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="3">
+      <c r="G4" s="37"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="23">
         <v>43</v>
       </c>
       <c r="K4" s="1"/>
@@ -1101,35 +1110,38 @@
       <c r="Z4" s="1"/>
     </row>
     <row r="5" spans="1:26" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="6">
+      <c r="A5" s="4">
         <v>3</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="7">
         <v>3291</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="7">
         <v>3295</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="7">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="8">
         <f t="shared" ref="E5:E14" si="1">E$15 * (D5/D$15)</f>
         <v>14.832167832167832</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="7">
         <v>10.7</v>
       </c>
-      <c r="G5" s="22">
+      <c r="G5" s="20">
         <f>SUM(E5,F5)</f>
         <v>25.532167832167829</v>
       </c>
-      <c r="H5" s="25">
-        <v>0</v>
+      <c r="H5" s="26">
+        <v>25.5</v>
       </c>
-      <c r="I5" s="1"/>
-      <c r="J5" s="3">
+      <c r="I5" s="29" t="str" cm="1">
+        <f t="array" ref="I5">_xlfn.IFS(ABS(G5-H5)&lt;0.1, "已收", G5&lt;H5, "多了", G5&gt;H5, "不够", H5=0, "没交")</f>
+        <v>已收</v>
+      </c>
+      <c r="J5" s="23">
         <v>6</v>
       </c>
       <c r="K5" s="1"/>
@@ -1150,35 +1162,38 @@
       <c r="Z5" s="1"/>
     </row>
     <row r="6" spans="1:26" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="6">
+      <c r="A6" s="4">
         <v>4</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="5">
         <v>1025</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="5">
         <v>1036</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="5">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="6">
         <f t="shared" si="1"/>
         <v>40.78846153846154</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="5">
         <v>10.7</v>
       </c>
-      <c r="G6" s="21">
+      <c r="G6" s="19">
         <f>SUM(E6,F6)</f>
         <v>51.488461538461536</v>
       </c>
-      <c r="H6" s="25">
-        <v>0</v>
+      <c r="H6" s="26">
+        <v>51.5</v>
       </c>
-      <c r="I6" s="1"/>
-      <c r="J6" s="3">
+      <c r="I6" s="29" t="str" cm="1">
+        <f t="array" ref="I6">_xlfn.IFS(ABS(G6-H6)&lt;0.1, "已收", G6&lt;H6, "多了", G6&gt;H6, "不够", H6=0, "没交")</f>
+        <v>已收</v>
+      </c>
+      <c r="J6" s="23">
         <v>14</v>
       </c>
       <c r="K6" s="1"/>
@@ -1199,35 +1214,38 @@
       <c r="Z6" s="1"/>
     </row>
     <row r="7" spans="1:26" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="6">
+      <c r="A7" s="4">
         <v>5</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="7">
         <v>3036</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="7">
         <v>3041</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="7">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="8">
         <f t="shared" si="1"/>
         <v>18.54020979020979</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="7">
         <v>10.7</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="20">
         <f t="shared" ref="G7:G14" si="2">SUM(E7,F7)</f>
         <v>29.240209790209789</v>
       </c>
-      <c r="H7" s="25">
-        <v>0</v>
+      <c r="H7" s="26">
+        <v>29.2</v>
       </c>
-      <c r="I7" s="1"/>
-      <c r="J7" s="3">
+      <c r="I7" s="29" t="str" cm="1">
+        <f t="array" ref="I7">_xlfn.IFS(ABS(G7-H7)&lt;0.1, "已收", G7&lt;H7, "多了", G7&gt;H7, "不够", H7=0, "没交")</f>
+        <v>已收</v>
+      </c>
+      <c r="J7" s="23">
         <v>8</v>
       </c>
       <c r="K7" s="1"/>
@@ -1248,35 +1266,38 @@
       <c r="Z7" s="1"/>
     </row>
     <row r="8" spans="1:26" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="6">
+      <c r="A8" s="4">
         <v>6</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="5">
         <v>4576</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="5">
         <v>4593</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="5">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="6">
         <f t="shared" si="1"/>
         <v>63.036713286713287</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="5">
         <v>10.7</v>
       </c>
-      <c r="G8" s="21">
+      <c r="G8" s="19">
         <f t="shared" si="2"/>
         <v>73.736713286713282</v>
       </c>
-      <c r="H8" s="25">
-        <v>0</v>
+      <c r="H8" s="26">
+        <v>73.7</v>
       </c>
-      <c r="I8" s="1"/>
-      <c r="J8" s="3">
+      <c r="I8" s="29" t="str" cm="1">
+        <f t="array" ref="I8">_xlfn.IFS(ABS(G8-H8)&lt;0.1, "已收", G8&lt;H8, "多了", G8&gt;H8, "不够", H8=0, "没交")</f>
+        <v>已收</v>
+      </c>
+      <c r="J8" s="23">
         <v>19</v>
       </c>
       <c r="K8" s="1"/>
@@ -1297,35 +1318,38 @@
       <c r="Z8" s="1"/>
     </row>
     <row r="9" spans="1:26" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="6">
+      <c r="A9" s="4">
         <v>7</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="7">
         <v>593</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="7">
         <v>596</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="7">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="8">
         <f t="shared" si="1"/>
         <v>11.124125874125875</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="7">
         <v>10.7</v>
       </c>
-      <c r="G9" s="22">
+      <c r="G9" s="20">
         <f t="shared" si="2"/>
         <v>21.824125874125876</v>
       </c>
-      <c r="H9" s="25">
-        <v>0</v>
+      <c r="H9" s="26">
+        <v>21.8</v>
       </c>
-      <c r="I9" s="1"/>
-      <c r="J9" s="3">
+      <c r="I9" s="29" t="str" cm="1">
+        <f t="array" ref="I9">_xlfn.IFS(ABS(G9-H9)&lt;0.1, "已收", G9&lt;H9, "多了", G9&gt;H9, "不够", H9=0, "没交")</f>
+        <v>已收</v>
+      </c>
+      <c r="J9" s="23">
         <v>6</v>
       </c>
       <c r="K9" s="1"/>
@@ -1346,35 +1370,38 @@
       <c r="Z9" s="1"/>
     </row>
     <row r="10" spans="1:26" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="6">
+      <c r="A10" s="4">
         <v>8</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="5">
         <v>4323</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="5">
         <v>4327</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="6">
         <f t="shared" si="1"/>
         <v>14.832167832167832</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="5">
         <v>10.7</v>
       </c>
-      <c r="G10" s="21">
+      <c r="G10" s="19">
         <f t="shared" si="2"/>
         <v>25.532167832167829</v>
       </c>
-      <c r="H10" s="25">
-        <v>0</v>
+      <c r="H10" s="26">
+        <v>25.5</v>
       </c>
-      <c r="I10" s="1"/>
-      <c r="J10" s="3">
+      <c r="I10" s="29" t="str" cm="1">
+        <f t="array" ref="I10">_xlfn.IFS(ABS(G10-H10)&lt;0.1, "已收", G10&lt;H10, "多了", G10&gt;H10, "不够", H10=0, "没交")</f>
+        <v>已收</v>
+      </c>
+      <c r="J10" s="23">
         <v>6</v>
       </c>
       <c r="K10" s="1"/>
@@ -1395,35 +1422,38 @@
       <c r="Z10" s="1"/>
     </row>
     <row r="11" spans="1:26" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="6">
+      <c r="A11" s="4">
         <v>9</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B11" s="7">
         <v>1879</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="7">
         <v>1898</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="7">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="8">
         <f t="shared" si="1"/>
         <v>70.4527972027972</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="7">
         <v>10.7</v>
       </c>
-      <c r="G11" s="22">
+      <c r="G11" s="20">
         <f t="shared" si="2"/>
         <v>81.152797202797203</v>
       </c>
-      <c r="H11" s="25">
-        <v>0</v>
+      <c r="H11" s="26">
+        <v>81.2</v>
       </c>
-      <c r="I11" s="1"/>
-      <c r="J11" s="3">
+      <c r="I11" s="29" t="str" cm="1">
+        <f t="array" ref="I11">_xlfn.IFS(ABS(G11-H11)&lt;0.1, "已收", G11&lt;H11, "多了", G11&gt;H11, "不够", H11=0, "没交")</f>
+        <v>已收</v>
+      </c>
+      <c r="J11" s="23">
         <v>30</v>
       </c>
       <c r="K11" s="1"/>
@@ -1444,35 +1474,38 @@
       <c r="Z11" s="1"/>
     </row>
     <row r="12" spans="1:26" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="6">
+      <c r="A12" s="4">
         <v>10</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="5">
         <v>1618</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="5">
         <v>1635</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="5">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="6">
         <f t="shared" si="1"/>
         <v>63.036713286713287</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="5">
         <v>10.7</v>
       </c>
-      <c r="G12" s="21">
+      <c r="G12" s="19">
         <f t="shared" si="2"/>
         <v>73.736713286713282</v>
       </c>
-      <c r="H12" s="25">
-        <v>0</v>
+      <c r="H12" s="26">
+        <v>73.7</v>
       </c>
-      <c r="I12" s="1"/>
-      <c r="J12" s="3">
+      <c r="I12" s="29" t="str" cm="1">
+        <f t="array" ref="I12">_xlfn.IFS(ABS(G12-H12)&lt;0.1, "已收", G12&lt;H12, "多了", G12&gt;H12, "不够", H12=0, "没交")</f>
+        <v>已收</v>
+      </c>
+      <c r="J12" s="23">
         <v>14</v>
       </c>
       <c r="K12" s="1"/>
@@ -1493,35 +1526,38 @@
       <c r="Z12" s="1"/>
     </row>
     <row r="13" spans="1:26" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="6">
+      <c r="A13" s="4">
         <v>11</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13" s="7">
         <v>1184</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="7">
         <v>1202</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="7">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="E13" s="10">
+      <c r="E13" s="8">
         <f t="shared" si="1"/>
         <v>66.744755244755254</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="7">
         <v>10.7</v>
       </c>
-      <c r="G13" s="22">
+      <c r="G13" s="20">
         <f t="shared" si="2"/>
         <v>77.444755244755257</v>
       </c>
-      <c r="H13" s="50">
+      <c r="H13" s="27">
         <v>77.400000000000006</v>
       </c>
-      <c r="I13" s="1"/>
-      <c r="J13" s="3">
+      <c r="I13" s="29" t="str" cm="1">
+        <f t="array" ref="I13">_xlfn.IFS(ABS(G13-H13)&lt;0.1, "已收", G13&lt;H13, "多了", G13&gt;H13, "不够", H13=0, "没交")</f>
+        <v>已收</v>
+      </c>
+      <c r="J13" s="23">
         <v>35</v>
       </c>
       <c r="K13" s="1"/>
@@ -1542,35 +1578,38 @@
       <c r="Z13" s="1"/>
     </row>
     <row r="14" spans="1:26" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="6">
+      <c r="A14" s="4">
         <v>12</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="5">
         <v>3896</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="5">
         <v>3905</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="5">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="6">
         <f t="shared" si="1"/>
         <v>33.372377622377627</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="5">
         <v>10.7</v>
       </c>
-      <c r="G14" s="21">
+      <c r="G14" s="19">
         <f t="shared" si="2"/>
         <v>44.07237762237763</v>
       </c>
-      <c r="H14" s="25">
-        <v>0</v>
+      <c r="H14" s="26">
+        <v>44.1</v>
       </c>
-      <c r="I14" s="1"/>
-      <c r="J14" s="3">
+      <c r="I14" s="29" t="str" cm="1">
+        <f t="array" ref="I14">_xlfn.IFS(ABS(G14-H14)&lt;0.1, "已收", G14&lt;H14, "多了", G14&gt;H14, "不够", H14=0, "没交")</f>
+        <v>已收</v>
+      </c>
+      <c r="J14" s="23">
         <v>13</v>
       </c>
       <c r="K14" s="1"/>
@@ -1591,31 +1630,34 @@
       <c r="Z14" s="1"/>
     </row>
     <row r="15" spans="1:26" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="15">
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="13">
         <f t="shared" ref="D15" si="3">SUM(D3:D14)</f>
         <v>143</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E15" s="10">
         <v>530.25</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="11">
         <v>128</v>
       </c>
-      <c r="G15" s="23">
+      <c r="G15" s="21">
         <f>SUM(E15:F15)</f>
         <v>658.25</v>
       </c>
-      <c r="H15" s="26">
+      <c r="H15" s="28">
         <f>SUM(H3:H14)</f>
-        <v>77.400000000000006</v>
+        <v>503.6</v>
       </c>
-      <c r="I15" s="1"/>
-      <c r="J15" s="3">
+      <c r="I15" s="29" t="str" cm="1">
+        <f t="array" ref="I15">_xlfn.IFS(ABS(G15-H15)&lt;0.1, "已收", G15&lt;H15, "多了", G15&gt;H15, "不够", H15=0, "没交")</f>
+        <v>不够</v>
+      </c>
+      <c r="J15" s="23">
         <f>SUM(J3:J14)</f>
         <v>189</v>
       </c>
@@ -1637,22 +1679,22 @@
       <c r="Z15" s="1"/>
     </row>
     <row r="16" spans="1:26" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="35" t="s">
+      <c r="A16" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="37" t="s">
+      <c r="B16" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="38"/>
-      <c r="D16" s="16" t="str">
+      <c r="C16" s="41"/>
+      <c r="D16" s="14" t="str">
         <f>_xlfn.CONCAT(D15, "方")</f>
         <v>143方</v>
       </c>
-      <c r="E16" s="42" t="s">
+      <c r="E16" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="F16" s="43"/>
-      <c r="G16" s="19">
+      <c r="F16" s="46"/>
+      <c r="G16" s="17">
         <f>E15/D15</f>
         <v>3.7080419580419579</v>
       </c>
@@ -1677,19 +1719,19 @@
       <c r="Z16" s="1"/>
     </row>
     <row r="17" spans="1:26" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="35"/>
-      <c r="B17" s="29" t="s">
+      <c r="A17" s="38"/>
+      <c r="B17" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="30"/>
-      <c r="D17" s="16" t="s">
+      <c r="C17" s="33"/>
+      <c r="D17" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="E17" s="39" t="s">
+      <c r="E17" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="F17" s="40"/>
-      <c r="G17" s="41"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="44"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -1711,23 +1753,23 @@
       <c r="Z17" s="1"/>
     </row>
     <row r="18" spans="1:26" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="36"/>
-      <c r="B18" s="31" t="s">
+      <c r="A18" s="39"/>
+      <c r="B18" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D18" s="44" t="str">
+      <c r="D18" s="47" t="str">
         <f>_xlfn.CONCAT("￥", E15)</f>
         <v>￥530.25</v>
       </c>
-      <c r="E18" s="45"/>
-      <c r="F18" s="48" t="str">
+      <c r="E18" s="48"/>
+      <c r="F18" s="51" t="str">
         <f>_xlfn.CONCAT("总：￥", G15)</f>
         <v>总：￥658.25</v>
       </c>
-      <c r="G18" s="49"/>
+      <c r="G18" s="52"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
@@ -1749,18 +1791,18 @@
       <c r="Z18" s="1"/>
     </row>
     <row r="19" spans="1:26" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="36"/>
-      <c r="B19" s="29"/>
-      <c r="C19" s="17" t="s">
+      <c r="A19" s="39"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="D19" s="46" t="str">
+      <c r="D19" s="49" t="str">
         <f>_xlfn.CONCAT("￥", F15)</f>
         <v>￥128</v>
       </c>
-      <c r="E19" s="47"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="49"/>
+      <c r="E19" s="50"/>
+      <c r="F19" s="51"/>
+      <c r="G19" s="52"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
@@ -29250,7 +29292,12 @@
       <c r="Z1000" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <protectedRanges>
+    <protectedRange sqref="H3:H14" name="区域1"/>
+  </protectedRanges>
+  <mergeCells count="13">
+    <mergeCell ref="I3:I4"/>
     <mergeCell ref="H3:H4"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B18:B19"/>
@@ -29265,6 +29312,11 @@
     <mergeCell ref="F18:G19"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="I3:I15">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="notEqual">
+      <formula>"已收"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>